--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -3973,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3982,6 +3982,11 @@
           <t>6/9/26</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>20/9/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3989,6 +3994,11 @@
           <t>Kerki Comp #41 - Maps by DeeDeeNaNaNa, PlusMicron, Kernkob &amp; Maki</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Kerki Comp #42 - Maps by Shadynook, IronDragon111000, variableferret</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4006,9 +4016,29 @@
           <t>Points</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
@@ -4023,6 +4053,14 @@
           <t>RoundNzt</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RoundNzt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4033,6 +4071,14 @@
           <t>Quickracer10</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kernkob</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4043,6 +4089,14 @@
           <t>PandaMane</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ZOMAN</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4053,6 +4107,14 @@
           <t>Lexer</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>microways</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4063,9 +4125,22 @@
           <t>Minkus</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>tatari_lover2008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>Finalists</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Finalists</t>
         </is>
@@ -4080,6 +4155,14 @@
           <t>Jake</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lexer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4090,6 +4173,14 @@
           <t>Murrl</t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>brrryy</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4100,6 +4191,11 @@
           <t>Eclipse135</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4110,12 +4206,34 @@
           <t>agix</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Tommygaming</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
@@ -4130,6 +4248,17 @@
       <c r="C16" t="n">
         <v>950</v>
       </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Minkus</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>958</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4143,6 +4272,17 @@
       <c r="C17" t="n">
         <v>865</v>
       </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Warsnac</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>903</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4156,6 +4296,17 @@
       <c r="C18" t="n">
         <v>805</v>
       </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>redal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4169,6 +4320,17 @@
       <c r="C19" t="n">
         <v>771</v>
       </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Revenger_19</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>779</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4182,6 +4344,17 @@
       <c r="C20" t="n">
         <v>734</v>
       </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Noxitu</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4195,6 +4368,17 @@
       <c r="C21" t="n">
         <v>715</v>
       </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Heart-TGV</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4208,6 +4392,17 @@
       <c r="C22" t="n">
         <v>666</v>
       </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>MALIYO</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>721</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4221,6 +4416,17 @@
       <c r="C23" t="n">
         <v>665</v>
       </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PlusMicron</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>657</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4234,6 +4440,17 @@
       <c r="C24" t="n">
         <v>661</v>
       </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>aizpun</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>652</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4247,6 +4464,17 @@
       <c r="C25" t="n">
         <v>626</v>
       </c>
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gimpel</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>638</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4260,6 +4488,17 @@
       <c r="C26" t="n">
         <v>619</v>
       </c>
+      <c r="G26" t="n">
+        <v>13</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>627</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4273,6 +4512,17 @@
       <c r="C27" t="n">
         <v>618</v>
       </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>wokonbike</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>592</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4286,6 +4536,17 @@
       <c r="C28" t="n">
         <v>617</v>
       </c>
+      <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DeeDeeNaNaNa</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>587</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4299,6 +4560,17 @@
       <c r="C29" t="n">
         <v>591</v>
       </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>kentback</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>546</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4312,6 +4584,17 @@
       <c r="C30" t="n">
         <v>576</v>
       </c>
+      <c r="G30" t="n">
+        <v>17</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Akane</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>531</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4325,6 +4608,17 @@
       <c r="C31" t="n">
         <v>560</v>
       </c>
+      <c r="G31" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>timesprout</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>520</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4338,6 +4632,17 @@
       <c r="C32" t="n">
         <v>557</v>
       </c>
+      <c r="G32" t="n">
+        <v>19</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>St Nicholas</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>478</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4351,6 +4656,17 @@
       <c r="C33" t="n">
         <v>521</v>
       </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>kkincaid97</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>454</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4364,6 +4680,17 @@
       <c r="C34" t="n">
         <v>496</v>
       </c>
+      <c r="G34" t="n">
+        <v>21</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SjorsTea</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4377,6 +4704,17 @@
       <c r="C35" t="n">
         <v>485</v>
       </c>
+      <c r="G35" t="n">
+        <v>22</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Aurum</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>397</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4390,6 +4728,17 @@
       <c r="C36" t="n">
         <v>408</v>
       </c>
+      <c r="G36" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Barn</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4403,6 +4752,17 @@
       <c r="C37" t="n">
         <v>313</v>
       </c>
+      <c r="G37" t="n">
+        <v>24</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M4DSCOTSM4N</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>320</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4416,6 +4776,17 @@
       <c r="C38" t="n">
         <v>292</v>
       </c>
+      <c r="G38" t="n">
+        <v>25</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DeiRex</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>275</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4429,6 +4800,17 @@
       <c r="C39" t="n">
         <v>236</v>
       </c>
+      <c r="G39" t="n">
+        <v>26</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Zeus</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4442,6 +4824,17 @@
       <c r="C40" t="n">
         <v>202</v>
       </c>
+      <c r="G40" t="n">
+        <v>27</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Flinzard</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4455,12 +4848,28 @@
       <c r="C41" t="n">
         <v>115</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nuisance</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
           <t>Nuisance</t>
         </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>justMaki</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>747</v>
       </c>
     </row>
     <row r="43">
@@ -4475,6 +4884,17 @@
       <c r="C43" t="n">
         <v>800</v>
       </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>IronDragon111000</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>588</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4487,6 +4907,17 @@
       </c>
       <c r="C44" t="n">
         <v>758</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Shadynook</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="45"/>

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>User Data</t>
+          <t>Zodiak</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3973,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4920,21 +4920,6 @@
         <v>384</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -3973,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>tatari_lover2008</t>
+          <t>Sterben</t>
         </is>
       </c>
     </row>
@@ -4920,6 +4920,21 @@
         <v>384</v>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -3973,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3987,6 +3987,11 @@
           <t>20/9/26</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>4/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3999,6 +4004,11 @@
           <t>Kerki Comp #42 - Maps by Shadynook, IronDragon111000, variableferret</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Kerki Comp #43 - Maps by Draugur, brrryy, justMaki</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4031,6 +4041,21 @@
           <t>Points</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4039,6 +4064,11 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
@@ -4061,6 +4091,14 @@
           <t>RoundNzt</t>
         </is>
       </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Kernkob</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4079,6 +4117,14 @@
           <t>Kernkob</t>
         </is>
       </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Lexer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4097,6 +4143,14 @@
           <t>ZOMAN</t>
         </is>
       </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Stick</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4115,6 +4169,14 @@
           <t>microways</t>
         </is>
       </c>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>RoundNzt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4133,6 +4195,14 @@
           <t>Sterben</t>
         </is>
       </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ZOMAN</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4141,6 +4211,11 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>Finalists</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Finalists</t>
         </is>
@@ -4163,6 +4238,14 @@
           <t>Lexer</t>
         </is>
       </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>microways</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4181,6 +4264,14 @@
           <t>brrryy</t>
         </is>
       </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Eclipse135</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4196,6 +4287,14 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>JakeAdjacent</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4217,6 +4316,14 @@
       <c r="I14" t="n">
         <v>1000</v>
       </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Minkus</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4234,6 +4341,11 @@
       </c>
       <c r="I15" t="n">
         <v>1000</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -4259,6 +4371,17 @@
       <c r="I16" t="n">
         <v>958</v>
       </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PlusMicron</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4283,6 +4406,17 @@
       <c r="I17" t="n">
         <v>903</v>
       </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Quickracer10</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4307,6 +4441,17 @@
       <c r="I18" t="n">
         <v>790</v>
       </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tommygaming</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4331,6 +4476,17 @@
       <c r="I19" t="n">
         <v>779</v>
       </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>agix</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>954</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4355,6 +4511,17 @@
       <c r="I20" t="n">
         <v>755</v>
       </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>897</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4379,6 +4546,17 @@
       <c r="I21" t="n">
         <v>723</v>
       </c>
+      <c r="M21" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ping</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>874</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4403,6 +4581,17 @@
       <c r="I22" t="n">
         <v>721</v>
       </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>redal</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4427,6 +4616,17 @@
       <c r="I23" t="n">
         <v>657</v>
       </c>
+      <c r="M23" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>AndMe</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>811</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4451,6 +4651,17 @@
       <c r="I24" t="n">
         <v>652</v>
       </c>
+      <c r="M24" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Diabler</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>682</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4475,6 +4686,17 @@
       <c r="I25" t="n">
         <v>638</v>
       </c>
+      <c r="M25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Noxitu</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>666</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4499,6 +4721,17 @@
       <c r="I26" t="n">
         <v>627</v>
       </c>
+      <c r="M26" t="n">
+        <v>11</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Heart-TGV</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>646</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4523,6 +4756,17 @@
       <c r="I27" t="n">
         <v>592</v>
       </c>
+      <c r="M27" t="n">
+        <v>12</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>DeeDeeNaNaNa</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>636</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4547,6 +4791,17 @@
       <c r="I28" t="n">
         <v>587</v>
       </c>
+      <c r="M28" t="n">
+        <v>13</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Matic_D</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>628</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4571,6 +4826,17 @@
       <c r="I29" t="n">
         <v>546</v>
       </c>
+      <c r="M29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Hang Chang-Pang</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>624</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4595,6 +4861,17 @@
       <c r="I30" t="n">
         <v>531</v>
       </c>
+      <c r="M30" t="n">
+        <v>15</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>aizpun</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>616</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4619,6 +4896,17 @@
       <c r="I31" t="n">
         <v>520</v>
       </c>
+      <c r="M31" t="n">
+        <v>16</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gilgool</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>611</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4643,6 +4931,17 @@
       <c r="I32" t="n">
         <v>478</v>
       </c>
+      <c r="M32" t="n">
+        <v>17</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>pannekoekbijter</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>606</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4667,6 +4966,17 @@
       <c r="I33" t="n">
         <v>454</v>
       </c>
+      <c r="M33" t="n">
+        <v>18</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>elekvault</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>598</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4691,6 +5001,17 @@
       <c r="I34" t="n">
         <v>420</v>
       </c>
+      <c r="M34" t="n">
+        <v>19</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Fly8oy</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>565</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4715,6 +5036,17 @@
       <c r="I35" t="n">
         <v>397</v>
       </c>
+      <c r="M35" t="n">
+        <v>20</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>wokonbike</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>546</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4739,6 +5071,17 @@
       <c r="I36" t="n">
         <v>340</v>
       </c>
+      <c r="M36" t="n">
+        <v>21</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SuperHeavy</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>542</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4763,6 +5106,17 @@
       <c r="I37" t="n">
         <v>320</v>
       </c>
+      <c r="M37" t="n">
+        <v>22</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>BrickEdwards</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>533</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4787,6 +5141,17 @@
       <c r="I38" t="n">
         <v>275</v>
       </c>
+      <c r="M38" t="n">
+        <v>23</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>kkincaid97</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>505</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4811,6 +5176,17 @@
       <c r="I39" t="n">
         <v>250</v>
       </c>
+      <c r="M39" t="n">
+        <v>24</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Zeus</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4835,6 +5211,17 @@
       <c r="I40" t="n">
         <v>165</v>
       </c>
+      <c r="M40" t="n">
+        <v>25</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>imagineaclevernamehere</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4853,6 +5240,17 @@
           <t>Nuisance</t>
         </is>
       </c>
+      <c r="M41" t="n">
+        <v>26</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>incredulouspotato</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>370</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4870,6 +5268,17 @@
       </c>
       <c r="I42" t="n">
         <v>747</v>
+      </c>
+      <c r="M42" t="n">
+        <v>27</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="43">
@@ -4895,6 +5304,17 @@
       <c r="I43" t="n">
         <v>588</v>
       </c>
+      <c r="M43" t="n">
+        <v>28</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>macermccoy92</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4919,10 +5339,51 @@
       <c r="I44" t="n">
         <v>384</v>
       </c>
-    </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
+      <c r="M44" t="n">
+        <v>29</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Don_E [GER]</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Nuisance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>justMaki</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>brrryy</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>662</v>
+      </c>
+    </row>
     <row r="48"/>
     <row r="49"/>
     <row r="50"/>

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Lexer</t>
+          <t>RoundNzt</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Stick</t>
+          <t>Lexer</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>RoundNzt</t>
+          <t>ZOMAN</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ZOMAN</t>
+          <t>Stick</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Eclipse135</t>
+          <t>Azalea</t>
         </is>
       </c>
     </row>

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -4088,7 +4088,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RoundNzt</t>
+          <t>Kernkob</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kernkob</t>
+          <t>RoundNzt</t>
         </is>
       </c>
       <c r="M6" t="n">

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -3996,7 +3996,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kerki Comp #41 - Maps by DeeDeeNaNaNa, PlusMicron, Kernkob &amp; Maki</t>
+          <t>Kerki Comp #41 - Maps by PlusMicron, DeeDeeNaNaNa, Maki &amp; Kernkob</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>JakeAdjacent</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eclipse135</t>
+          <t>Azalea</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AndMe18</t>
+          <t>AndMe</t>
         </is>
       </c>
       <c r="C32" t="n">

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>1089</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>1068</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PlusMicron</t>
+          <t>Tommygaming</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1000</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="17">
@@ -4411,11 +4411,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Quickracer10</t>
+          <t>PlusMicron</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1000</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="18">
@@ -4446,11 +4446,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tommygaming</t>
+          <t>Quickracer10</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="19">

--- a/Kerki Comp Results 31+.xlsx
+++ b/Kerki Comp Results 31+.xlsx
@@ -3973,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3992,6 +3992,11 @@
           <t>4/10/26</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>18/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4009,6 +4014,11 @@
           <t>Kerki Comp #43 - Maps by Draugur, brrryy, justMaki</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Kerki Comp #44 - Maps by redal, Hellmet, Diabler</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4056,6 +4066,21 @@
           <t>Points</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4069,6 +4094,11 @@
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
@@ -4099,6 +4129,14 @@
           <t>Kernkob</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ZOMAN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4125,6 +4163,14 @@
           <t>RoundNzt</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Lexer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4151,6 +4197,14 @@
           <t>Lexer</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stick</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4177,6 +4231,14 @@
           <t>ZOMAN</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>RoundNzt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4203,6 +4265,14 @@
           <t>Stick</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Minkus</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4216,6 +4286,11 @@
         </is>
       </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>Finalists</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Finalists</t>
         </is>
@@ -4246,6 +4321,14 @@
           <t>microways</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Quickracer10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4272,6 +4355,14 @@
           <t>Azalea</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>brrryy</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4295,6 +4386,14 @@
           <t>JakeAdjacent</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>PlusMicron</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4324,6 +4423,14 @@
           <t>Minkus</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Murrl</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4343,6 +4450,11 @@
         <v>1068</v>
       </c>
       <c r="M15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -4382,6 +4494,17 @@
       <c r="O16" t="n">
         <v>1097</v>
       </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>agix</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>1076</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4417,6 +4540,17 @@
       <c r="O17" t="n">
         <v>1015</v>
       </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Warsnac</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>923</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4452,6 +4586,17 @@
       <c r="O18" t="n">
         <v>1005</v>
       </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Heart-TGV</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>920</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4487,6 +4632,17 @@
       <c r="O19" t="n">
         <v>954</v>
       </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>871</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4522,6 +4678,17 @@
       <c r="O20" t="n">
         <v>897</v>
       </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>variableferret</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>826</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4557,6 +4724,17 @@
       <c r="O21" t="n">
         <v>874</v>
       </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>MALIYO</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>809</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4592,6 +4770,17 @@
       <c r="O22" t="n">
         <v>855</v>
       </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Sterben</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4627,6 +4816,17 @@
       <c r="O23" t="n">
         <v>811</v>
       </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>BB_Benji</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>772</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4662,6 +4862,17 @@
       <c r="O24" t="n">
         <v>682</v>
       </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>DeiRex</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>772</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4697,6 +4908,17 @@
       <c r="O25" t="n">
         <v>666</v>
       </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Noxitu</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>765</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4732,6 +4954,17 @@
       <c r="O26" t="n">
         <v>646</v>
       </c>
+      <c r="S26" t="n">
+        <v>11</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Redstony</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4767,6 +5000,17 @@
       <c r="O27" t="n">
         <v>636</v>
       </c>
+      <c r="S27" t="n">
+        <v>12</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>DeeDeeNaNaNa</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>719</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4802,6 +5046,17 @@
       <c r="O28" t="n">
         <v>628</v>
       </c>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>aizpun</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>661</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4837,6 +5092,17 @@
       <c r="O29" t="n">
         <v>624</v>
       </c>
+      <c r="S29" t="n">
+        <v>14</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Hang Chang-Pang</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>644</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4872,6 +5138,17 @@
       <c r="O30" t="n">
         <v>616</v>
       </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>IronDragon111000</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>644</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4907,6 +5184,17 @@
       <c r="O31" t="n">
         <v>611</v>
       </c>
+      <c r="S31" t="n">
+        <v>16</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Mr Croc</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>636</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4942,6 +5230,17 @@
       <c r="O32" t="n">
         <v>606</v>
       </c>
+      <c r="S32" t="n">
+        <v>17</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>wokonbike</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>623</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4977,6 +5276,17 @@
       <c r="O33" t="n">
         <v>598</v>
       </c>
+      <c r="S33" t="n">
+        <v>18</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Matic_D</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>619</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5012,6 +5322,17 @@
       <c r="O34" t="n">
         <v>565</v>
       </c>
+      <c r="S34" t="n">
+        <v>19</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>BrickEdwards</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>566</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5047,6 +5368,17 @@
       <c r="O35" t="n">
         <v>546</v>
       </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Romans138</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>555</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5082,6 +5414,17 @@
       <c r="O36" t="n">
         <v>542</v>
       </c>
+      <c r="S36" t="n">
+        <v>21</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Ruckooe</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>553</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5117,6 +5460,17 @@
       <c r="O37" t="n">
         <v>533</v>
       </c>
+      <c r="S37" t="n">
+        <v>22</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>timesprout</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>551</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5152,6 +5506,17 @@
       <c r="O38" t="n">
         <v>505</v>
       </c>
+      <c r="S38" t="n">
+        <v>23</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>That Weird Guy</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5187,6 +5552,17 @@
       <c r="O39" t="n">
         <v>420</v>
       </c>
+      <c r="S39" t="n">
+        <v>24</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>pannekoekbijter</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5222,6 +5598,17 @@
       <c r="O40" t="n">
         <v>385</v>
       </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Orb Bee Bob</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>535</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5251,6 +5638,17 @@
       <c r="O41" t="n">
         <v>370</v>
       </c>
+      <c r="S41" t="n">
+        <v>26</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Akane</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>525</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5279,6 +5677,17 @@
       </c>
       <c r="O42" t="n">
         <v>310</v>
+      </c>
+      <c r="S42" t="n">
+        <v>27</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Fly8oy</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="43">
@@ -5315,6 +5724,17 @@
       <c r="O43" t="n">
         <v>270</v>
       </c>
+      <c r="S43" t="n">
+        <v>28</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>HighPing_Enjoyer</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>490</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5350,12 +5770,34 @@
       <c r="O44" t="n">
         <v>135</v>
       </c>
+      <c r="S44" t="n">
+        <v>29</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>マイゴデス</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="45">
       <c r="M45" t="inlineStr">
         <is>
           <t>Nuisance</t>
         </is>
+      </c>
+      <c r="S45" t="n">
+        <v>30</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Aurum</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>456</v>
       </c>
     </row>
     <row r="46">
@@ -5370,6 +5812,17 @@
       <c r="O46" t="n">
         <v>1330</v>
       </c>
+      <c r="S46" t="n">
+        <v>31</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Barn</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>430</v>
+      </c>
     </row>
     <row r="47">
       <c r="M47" t="n">
@@ -5383,19 +5836,168 @@
       <c r="O47" t="n">
         <v>662</v>
       </c>
-    </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
+      <c r="S47" t="n">
+        <v>32</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>SouthMango</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="S48" t="n">
+        <v>33</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>kkincaid97</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="S49" t="n">
+        <v>34</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>FINSTER83</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="S50" t="n">
+        <v>35</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Freud</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="S51" t="n">
+        <v>36</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>NyxeonFox</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="S52" t="n">
+        <v>37</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Ylvs</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="S53" t="n">
+        <v>38</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>gilgool</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="S54" t="n">
+        <v>39</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="S55" t="n">
+        <v>40</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Feral_Ratt</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Nuisance</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>justMaki</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Diabler</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="S59" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Hellmet</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>451</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
